--- a/main/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/main/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:15:18+00:00</t>
+    <t>2026-04-10T13:47:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/main/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:47:19+00:00</t>
+    <t>2026-04-10T14:43:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/main/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T14:43:25+00:00</t>
+    <t>2026-06-23T08:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
